--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2020_T1_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2020_T1_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>77</t>
+    <t>56</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.63e+05</t>
-  </si>
-  <si>
-    <t>(69336.318)</t>
-  </si>
-  <si>
-    <t>498.438</t>
-  </si>
-  <si>
-    <t>(34.442)</t>
-  </si>
-  <si>
-    <t>3.606</t>
-  </si>
-  <si>
-    <t>(0.046)</t>
-  </si>
-  <si>
-    <t>10.256</t>
-  </si>
-  <si>
-    <t>(1.781)</t>
-  </si>
-  <si>
-    <t>88.390</t>
-  </si>
-  <si>
-    <t>(0.470)</t>
-  </si>
-  <si>
-    <t>1.04e+06</t>
-  </si>
-  <si>
-    <t>(54360.894)</t>
-  </si>
-  <si>
-    <t>2.506</t>
-  </si>
-  <si>
-    <t>(0.127)</t>
-  </si>
-  <si>
-    <t>3.346</t>
-  </si>
-  <si>
-    <t>(0.445)</t>
-  </si>
-  <si>
-    <t>33.731</t>
-  </si>
-  <si>
-    <t>(3.542)</t>
-  </si>
-  <si>
-    <t>0.949</t>
-  </si>
-  <si>
-    <t>(0.025)</t>
-  </si>
-  <si>
-    <t>38</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>7.19e+05</t>
-  </si>
-  <si>
-    <t>(1.39e+05)</t>
-  </si>
-  <si>
-    <t>480.724</t>
-  </si>
-  <si>
-    <t>(54.681)</t>
-  </si>
-  <si>
-    <t>3.339</t>
-  </si>
-  <si>
-    <t>(0.059)</t>
-  </si>
-  <si>
-    <t>27.868</t>
-  </si>
-  <si>
-    <t>(4.181)</t>
-  </si>
-  <si>
-    <t>91.273</t>
-  </si>
-  <si>
-    <t>(0.485)</t>
-  </si>
-  <si>
-    <t>1.36e+06</t>
-  </si>
-  <si>
-    <t>(73920.664)</t>
-  </si>
-  <si>
-    <t>3.342</t>
-  </si>
-  <si>
-    <t>(0.151)</t>
-  </si>
-  <si>
-    <t>6.158</t>
-  </si>
-  <si>
-    <t>(0.632)</t>
-  </si>
-  <si>
-    <t>43.711</t>
-  </si>
-  <si>
-    <t>(3.495)</t>
+    <t>6.98e+05</t>
+  </si>
+  <si>
+    <t>(1.00e+05)</t>
+  </si>
+  <si>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
+  </si>
+  <si>
+    <t>1.38e+06</t>
+  </si>
+  <si>
+    <t>(57218.217)</t>
+  </si>
+  <si>
+    <t>3.352</t>
+  </si>
+  <si>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.56e+05</t>
-  </si>
-  <si>
-    <t>-17.714</t>
-  </si>
-  <si>
-    <t>-0.267***</t>
-  </si>
-  <si>
-    <t>17.612***</t>
-  </si>
-  <si>
-    <t>2.883***</t>
-  </si>
-  <si>
-    <t>3.12e+05***</t>
-  </si>
-  <si>
-    <t>0.836***</t>
-  </si>
-  <si>
-    <t>2.812***</t>
-  </si>
-  <si>
-    <t>9.980*</t>
-  </si>
-  <si>
-    <t>0.051</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
+  </si>
+  <si>
+    <t>0.071**</t>
   </si>
 </sst>
 </file>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2020_T1_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2020_T1_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>78</t>
+  </si>
+  <si>
+    <t>77</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>60</t>
+    <t>5.63e+05</t>
+  </si>
+  <si>
+    <t>(69336.318)</t>
+  </si>
+  <si>
+    <t>498.438</t>
+  </si>
+  <si>
+    <t>(34.442)</t>
+  </si>
+  <si>
+    <t>3.606</t>
+  </si>
+  <si>
+    <t>(0.046)</t>
+  </si>
+  <si>
+    <t>10.256</t>
+  </si>
+  <si>
+    <t>(1.781)</t>
+  </si>
+  <si>
+    <t>88.390</t>
+  </si>
+  <si>
+    <t>(0.470)</t>
+  </si>
+  <si>
+    <t>1.04e+06</t>
+  </si>
+  <si>
+    <t>(54360.894)</t>
+  </si>
+  <si>
+    <t>2.506</t>
+  </si>
+  <si>
+    <t>(0.127)</t>
+  </si>
+  <si>
+    <t>3.346</t>
+  </si>
+  <si>
+    <t>(0.445)</t>
+  </si>
+  <si>
+    <t>33.731</t>
+  </si>
+  <si>
+    <t>(3.542)</t>
+  </si>
+  <si>
+    <t>0.949</t>
+  </si>
+  <si>
+    <t>(0.025)</t>
+  </si>
+  <si>
+    <t>38</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.98e+05</t>
-  </si>
-  <si>
-    <t>(1.00e+05)</t>
-  </si>
-  <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
-  </si>
-  <si>
-    <t>1.38e+06</t>
-  </si>
-  <si>
-    <t>(57218.217)</t>
-  </si>
-  <si>
-    <t>3.352</t>
-  </si>
-  <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>7.19e+05</t>
+  </si>
+  <si>
+    <t>(1.39e+05)</t>
+  </si>
+  <si>
+    <t>480.724</t>
+  </si>
+  <si>
+    <t>(54.681)</t>
+  </si>
+  <si>
+    <t>3.339</t>
+  </si>
+  <si>
+    <t>(0.059)</t>
+  </si>
+  <si>
+    <t>27.868</t>
+  </si>
+  <si>
+    <t>(4.181)</t>
+  </si>
+  <si>
+    <t>91.273</t>
+  </si>
+  <si>
+    <t>(0.485)</t>
+  </si>
+  <si>
+    <t>1.36e+06</t>
+  </si>
+  <si>
+    <t>(73920.664)</t>
+  </si>
+  <si>
+    <t>3.342</t>
+  </si>
+  <si>
+    <t>(0.151)</t>
+  </si>
+  <si>
+    <t>6.158</t>
+  </si>
+  <si>
+    <t>(0.632)</t>
+  </si>
+  <si>
+    <t>43.711</t>
+  </si>
+  <si>
+    <t>(3.495)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
-  </si>
-  <si>
-    <t>0.071**</t>
+    <t>1.56e+05</t>
+  </si>
+  <si>
+    <t>-17.714</t>
+  </si>
+  <si>
+    <t>-0.267***</t>
+  </si>
+  <si>
+    <t>17.612***</t>
+  </si>
+  <si>
+    <t>2.883***</t>
+  </si>
+  <si>
+    <t>3.12e+05***</t>
+  </si>
+  <si>
+    <t>0.836***</t>
+  </si>
+  <si>
+    <t>2.812***</t>
+  </si>
+  <si>
+    <t>9.980*</t>
+  </si>
+  <si>
+    <t>0.051</t>
   </si>
 </sst>
 </file>
